--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:37</t>
+    <t xml:space="preserve">2026-09-09 22:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:23</t>
+    <t xml:space="preserve">2026-09-12 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
@@ -48,6 +48,9 @@
     <t xml:space="preserve">Paihuano</t>
   </si>
   <si>
+    <t xml:space="preserve">Canela</t>
+  </si>
+  <si>
     <t xml:space="preserve">La Serena</t>
   </si>
   <si>
@@ -57,9 +60,6 @@
     <t xml:space="preserve">Combarbalá</t>
   </si>
   <si>
-    <t xml:space="preserve">Canela</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vicuña</t>
   </si>
   <si>
@@ -72,12 +72,12 @@
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
+    <t xml:space="preserve">Salamanca</t>
+  </si>
+  <si>
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Salamanca</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:40</t>
+    <t xml:space="preserve">2026-09-24 00:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>58.62</v>
+        <v>26.05</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46.73</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>41.53</v>
+        <v>17.21</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>40.4</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="6">
@@ -585,13 +585,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4101</v>
+        <v>4202</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35.4</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="7">
@@ -602,13 +602,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4203</v>
+        <v>4101</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34.11</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="8">
@@ -619,13 +619,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4302</v>
+        <v>4203</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34.09</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="9">
@@ -636,13 +636,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4202</v>
+        <v>4302</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>33.69</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="10">
@@ -650,16 +650,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4102</v>
+        <v>4106</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>31.43</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="11">
@@ -667,16 +667,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4106</v>
+        <v>4102</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>30.93</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="12">
@@ -693,7 +693,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28.65</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26.55</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +727,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>22.89</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="15">
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4201</v>
+        <v>4204</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21.18</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="16">
@@ -755,13 +755,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4204</v>
+        <v>4201</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>20.88</v>
+        <v>9.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:17</t>
+    <t xml:space="preserve">2026-09-27 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:07</t>
+    <t xml:space="preserve">2026-09-29 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>26.05</v>
+        <v>260.49</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20.98</v>
+        <v>209.77</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17.21</v>
+        <v>172.13</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16.89</v>
+        <v>168.93</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15.37</v>
+        <v>153.71</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15.12</v>
+        <v>151.21</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14.27</v>
+        <v>142.75</v>
       </c>
     </row>
     <row r="9">
@@ -642,7 +642,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14.09</v>
+        <v>140.94</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12.96</v>
+        <v>129.57</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12.92</v>
+        <v>129.2</v>
       </c>
     </row>
     <row r="12">
@@ -693,7 +693,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11.9</v>
+        <v>119.05</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11.06</v>
+        <v>110.56</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +727,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9.33</v>
+        <v>93.28</v>
       </c>
     </row>
     <row r="15">
@@ -744,7 +744,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9.31</v>
+        <v>93.06</v>
       </c>
     </row>
     <row r="16">
@@ -761,7 +761,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9.12</v>
+        <v>91.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:01</t>
+    <t xml:space="preserve">2026-10-01 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:26</t>
+    <t xml:space="preserve">2026-10-02 13:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:05</t>
+    <t xml:space="preserve">2026-10-04 07:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:57</t>
+    <t xml:space="preserve">2026-10-05 07:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
